--- a/report-007-manual-007.xlsx
+++ b/report-007-manual-007.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>{"baseline_commit": "afeac4bb28f77132a45cd3695e183d232233e7b3", "fix_commit": "fb4808927d55ad6d4ff43b8e35af07f2e6c323f7", "fix_passed": true, "red_failed": true, "test_commit": "632b0fe92cad53b15c5f63a0e89edc637c92447b"}</t>
+          <t>{"post_fix": {"commit": "fb4808927d55ad6d4ff43b8e35af07f2e6c323f7", "result": "green", "trajectory_url": "未生成"}, "pre_fix": {"commit": "632b0fe92cad53b15c5f63a0e89edc637c92447b", "result": "red", "trajectory_url": "未生成"}}</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
